--- a/docs/테이블설계서_BS_SERVICE.xlsx
+++ b/docs/테이블설계서_BS_SERVICE.xlsx
@@ -54,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,7 +125,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -133,6 +138,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -502,16 +510,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -534,17 +543,18 @@
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>논리명</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>서비스 Catalog</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -559,17 +569,18 @@
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>DBMS</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -584,17 +595,18 @@
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §7.2/7.3</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -624,10 +636,15 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
+          <t>유효값(코드값)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
@@ -661,10 +678,15 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>서비스 고유 식별자(대문자·점 구분, 전역 유일, Handler ID와 일치). 실행/조회의 조회키 [핵심 로직]</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
@@ -694,10 +716,15 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
           <t>서비스 표시명(화면 목록/상세 표시용)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>결산 진행상태 조회</t>
         </is>
@@ -725,12 +752,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>CLOSING, JOURNAL, EXPENSE, STATEMENT, CSM (파일럿 5개 도메인 기준, 확장 가능)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>업무 도메인 분류 코드(그룹핑·표시용, 로직 분기 없음)</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>CLOSING</t>
         </is>
@@ -758,12 +790,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>서비스 성격 READ/ACTION (CHECK 제약). 콘솔 등록 시 값 검증에만 사용</t>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>READ(조회), ACTION(실행)  ※CHECK 제약</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>서비스 성격. 콘솔 등록 시 값 검증에만 사용(실행 분기 없음)</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>READ</t>
         </is>
@@ -791,12 +828,17 @@
           <t>'IFRS17'</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>IFRS17 (Phase 1 기본·사실상 고정, 확장 가능)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>서비스 원천 시스템(카탈로그·응답 메타로 전달, 표시용)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>IFRS17</t>
         </is>
@@ -826,10 +868,15 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
           <t>서비스 업무 책임 부서(Owner)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>정보기술팀</t>
         </is>
@@ -857,12 +904,17 @@
           <t>'Y'</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Y(사용), N(미사용)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>서비스 사용 여부(N이면 신규 호출 즉시 차단). 실행 게이트 [핵심 로직]</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -892,10 +944,15 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
           <t>최초 등록 일시(감사)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>2026-07-14 09:00:00</t>
         </is>
@@ -925,10 +982,15 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
           <t>최초 등록자 ID(운영자, 감사)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
@@ -958,10 +1020,15 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
           <t>최종 수정 일시(감사)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>2026-07-30 10:00:00</t>
         </is>
@@ -991,32 +1058,37 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
           <t>최종 수정자 ID(운영자, 감사)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>E12345</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>범례: [핵심 로직] = 실제 실행/조회 흐름의 분기·판단에 사용 (그 외 컬럼은 저장·표시·감사 용도) · PK 컬럼은 음영 표시</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>범례: 유효값(코드값) 열은 코드성 컬럼만 기재(연녹 음영) · [핵심 로직]=실제 실행/조회 분기에 사용 · PK 컬럼 음영 · '-'=자유값/해당없음</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
